--- a/files/Personal.xlsx
+++ b/files/Personal.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salva\Documents\Personal\Personal\Select_Shop\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3B37677-CF3E-4CC3-A65C-471923D17141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7312C41D-AE97-4CFC-8ABD-ECD14E785701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9BFC2C5D-E8F6-4E7C-A06B-114FA68585F0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CCE7E193-CC7F-467D-BEA4-4770926175D0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Personal" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,22 +35,71 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+  <si>
+    <t>Marbete</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Piezas</t>
+  </si>
+  <si>
+    <t>Cajas</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Llegada</t>
+  </si>
+  <si>
+    <t>Contenedor</t>
+  </si>
+  <si>
+    <t>UPC</t>
+  </si>
+  <si>
+    <t>Master Pack</t>
+  </si>
+  <si>
+    <t>Proveedor</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,8 +114,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,10 +461,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C350BB32-9EB3-417B-BA63-023AF4EE37CF}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA8A10B-44E4-44D1-AACD-5488F5E58279}">
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>